--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260824.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260824.xlsx
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>199,392,618</t>
+          <t>74,981,431</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>74,981,431</t>
+          <t>199,392,618</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>148,029,020</t>
+          <t>22,584,009</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>25,493,288</t>
+          <t>148,029,020</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>22,584,009</t>
+          <t>25,493,288</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
